--- a/tests/resources/test_data/TestCases.xlsx
+++ b/tests/resources/test_data/TestCases.xlsx
@@ -60,16 +60,16 @@
     <t xml:space="preserve">Ahoj,babi</t>
   </si>
   <si>
-    <t xml:space="preserve">Ahoj babi</t>
+    <t xml:space="preserve">Ahoj, babi</t>
   </si>
   <si>
     <t xml:space="preserve">Wrong format viz</t>
   </si>
   <si>
-    <t xml:space="preserve">viz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">viz</t>
+    <t xml:space="preserve">Ahoj,babi,znovu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahoj, babi, znovu</t>
   </si>
   <si>
     <t xml:space="preserve">default</t>
@@ -313,7 +313,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="20.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="26.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="32.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="11.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20.76"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="1" width="11.53"/>
   </cols>
   <sheetData>

--- a/tests/resources/test_data/TestCases.xlsx
+++ b/tests/resources/test_data/TestCases.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
   <si>
     <t xml:space="preserve">*** Test Cases ***</t>
   </si>
@@ -43,6 +43,9 @@
   </si>
   <si>
     <t xml:space="preserve">${expected}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${fixes_count}</t>
   </si>
   <si>
     <t xml:space="preserve">Space after comma</t>
@@ -307,7 +310,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="20.76"/>
@@ -315,7 +318,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="32.05"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20.76"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12.84"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -340,51 +344,60 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -411,7 +424,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -438,10 +451,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/tests/resources/test_data/TestCases.xlsx
+++ b/tests/resources/test_data/TestCases.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="42">
   <si>
     <t xml:space="preserve">*** Test Cases ***</t>
   </si>
@@ -75,7 +75,79 @@
     <t xml:space="preserve">Ahoj, babi, znovu</t>
   </si>
   <si>
-    <t xml:space="preserve">default</t>
+    <t xml:space="preserve">Czech (traditional rules)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulgarian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Croatian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dutch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English (UK)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English (US)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finnish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">French</t>
+  </si>
+  <si>
+    <t xml:space="preserve">German (Germany)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hungarian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Irish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latvian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lithuanian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maltese</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portuguese</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romanian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovenian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spanish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swedish</t>
   </si>
 </sst>
 </file>
@@ -401,6 +473,20 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A1:A1003" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D2:D100" type="list">
+      <formula1>languages!$A$1:$A$26</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E2:E100" type="list">
+      <formula1>preferences!$A$1:$A$50</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -416,15 +502,140 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="26.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="26.42"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -453,9 +664,7 @@
       <c r="A1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="B1" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/tests/resources/test_data/TestCases.xlsx
+++ b/tests/resources/test_data/TestCases.xlsx
@@ -5,12 +5,13 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="tc" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="languages" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="preferences" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Sheet4" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="58">
   <si>
     <t xml:space="preserve">*** Test Cases ***</t>
   </si>
@@ -148,6 +149,54 @@
   </si>
   <si>
     <t xml:space="preserve">Swedish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">add test entru není exit </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 tis. € (Czech, Slovenian)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 tys. € (Polish)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 mil. € (many languages)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 млн. (Bulgarian)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 mio. (Danish)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210 miljard = 210 mld. (Dutch)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 Mio. (German)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 τρισ. (Greek)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 mrd (Hungarian)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 tūkst. (Lithuanian, Latvian)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 tn (Swedish)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 tuh (Estonian)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 tril., 1 mie, 10 mii, 1 milion (Romanian)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all languages</t>
   </si>
 </sst>
 </file>
@@ -238,7 +287,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -259,6 +308,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -269,6 +326,201 @@
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>528480</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>80280</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Image 1"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="13993560" cy="3981600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>679680</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>5040</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="812880" y="4551840"/>
+          <a:ext cx="4743720" cy="1142640"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>197280</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>50400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Image 3"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="812880" y="5852160"/>
+          <a:ext cx="5886720" cy="5200920"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>529920</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>59760</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Image 4"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="812880" y="12140640"/>
+          <a:ext cx="14807880" cy="5099040"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>709200</xdr:colOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>157320</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Image 5"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="812880" y="17505000"/>
+          <a:ext cx="14174280" cy="9098280"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -382,7 +634,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="20.76"/>
@@ -451,7 +703,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>9</v>
@@ -471,6 +723,63 @@
       <c r="H3" s="1" t="n">
         <v>2</v>
       </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F4" s="0"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F5" s="0"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F6" s="0"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F7" s="0"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F8" s="0"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F9" s="0"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F10" s="0"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F11" s="0"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F12" s="0"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F13" s="0"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F14" s="0"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F15" s="0"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F16" s="0"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F17" s="0"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F18" s="0"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F19" s="0"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F20" s="0"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F21" s="0"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F22" s="0"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -675,4 +984,139 @@
     <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FFFF00FF"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B27:L57"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="41.13"/>
+  </cols>
+  <sheetData>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="0" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="34" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K39" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="23.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K40" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="34" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K41" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="23.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K42" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="23.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K43" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="34" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K44" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="23.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K45" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="23.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K46" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="23.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K47" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="34" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K48" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="23.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K49" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="23.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K50" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K51" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K52" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L52" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K53" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L53" s="6"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K54" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L54" s="6"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K55" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L55" s="6"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K56" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L56" s="6"/>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K57" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L57" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="L52:L57"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/tests/resources/test_data/TestCases.xlsx
+++ b/tests/resources/test_data/TestCases.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="tc" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="119">
   <si>
     <t xml:space="preserve">*** Test Cases ***</t>
   </si>
@@ -37,9 +37,6 @@
     <t xml:space="preserve">${language}</t>
   </si>
   <si>
-    <t xml:space="preserve">${preference}</t>
-  </si>
-  <si>
     <t xml:space="preserve">${given}</t>
   </si>
   <si>
@@ -49,7 +46,10 @@
     <t xml:space="preserve">${fixes_count}</t>
   </si>
   <si>
-    <t xml:space="preserve">Space after comma</t>
+    <t xml:space="preserve">Cz-academic: Space after comma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doc1</t>
   </si>
   <si>
     <t xml:space="preserve">demo</t>
@@ -58,97 +58,280 @@
     <t xml:space="preserve">Czech (academic rules)</t>
   </si>
   <si>
+    <t xml:space="preserve">Ahoj,babi, PhD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahoj, babi, PhD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cz-academic: Spaces after comma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doc2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahoj,babi,znovu, PhD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahoj, babi, znovu, PhD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cz-trad: Space after comma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doc3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czech (traditional rules)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahoj,babi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahoj, babi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cz-trad: Spaces after comma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doc4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahoj,babi,znovu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahoj, babi, znovu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-czech-academic-rules.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-czech-academic-rules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-czech-traditional-rules.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-czech-traditional-rules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulgarian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-bulgarian.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-bulgarian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Croatian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-croatian.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-croatian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-danish.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-danish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dutch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-dutch.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-dutch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English (UK)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-english-uk.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-english-uk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English (US)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-english-us.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-english-us</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-estonian.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-estonian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finnish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-finnish.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-finnish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">French</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-french.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-french</t>
+  </si>
+  <si>
+    <t xml:space="preserve">German (Germany)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-german-germany.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-german-germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-greek.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-greek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hungarian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-hungarian.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-hungarian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Irish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-irish.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-irish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-italian.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-italian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latvian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-latvian.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-latvian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lithuanian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-lithuanian.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-lithuanian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maltese</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-maltese.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-maltese</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-polish.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-polish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portuguese</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-portuguese.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-portuguese</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romanian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-romanian.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-romanian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-slovak.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-slovak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovenian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-slovenian.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-slovenian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spanish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-spanish.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-spanish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swedish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-swedish.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;test-swedish</t>
+  </si>
+  <si>
     <t xml:space="preserve">TEST_AUT_ReferenceSet_cz_ak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ahoj,babi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ahoj, babi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wrong format viz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ahoj,babi,znovu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ahoj, babi, znovu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czech (traditional rules)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulgarian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Croatian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Danish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dutch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">English (UK)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">English (US)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finnish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">French</t>
-  </si>
-  <si>
-    <t xml:space="preserve">German (Germany)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hungarian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Irish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Italian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latvian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lithuanian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maltese</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portuguese</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Romanian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slovak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slovenian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spanish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Swedish</t>
   </si>
   <si>
     <t xml:space="preserve">add test entru není exit </t>
@@ -308,11 +491,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -339,9 +522,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>528480</xdr:colOff>
+      <xdr:colOff>528120</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>80280</xdr:rowOff>
+      <xdr:rowOff>79920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -355,7 +538,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="13993560" cy="3981600"/>
+          <a:ext cx="13993200" cy="3981240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -377,9 +560,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>679680</xdr:colOff>
+      <xdr:colOff>679320</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>5040</xdr:rowOff>
+      <xdr:rowOff>4680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -393,7 +576,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="812880" y="4551840"/>
-          <a:ext cx="4743720" cy="1142640"/>
+          <a:ext cx="4743360" cy="1142280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -415,9 +598,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>197280</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>50400</xdr:rowOff>
+      <xdr:colOff>196920</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>161280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -431,7 +614,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="812880" y="5852160"/>
-          <a:ext cx="5886720" cy="5200920"/>
+          <a:ext cx="5886360" cy="5200560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -453,9 +636,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>529920</xdr:colOff>
+      <xdr:colOff>529560</xdr:colOff>
       <xdr:row>90</xdr:row>
-      <xdr:rowOff>59760</xdr:rowOff>
+      <xdr:rowOff>59400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -468,8 +651,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="812880" y="12140640"/>
-          <a:ext cx="14807880" cy="5099040"/>
+          <a:off x="812880" y="9591120"/>
+          <a:ext cx="14807520" cy="5098680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -491,9 +674,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>709200</xdr:colOff>
+      <xdr:colOff>708840</xdr:colOff>
       <xdr:row>147</xdr:row>
-      <xdr:rowOff>157320</xdr:rowOff>
+      <xdr:rowOff>156960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -506,8 +689,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="812880" y="17505000"/>
-          <a:ext cx="14174280" cy="9098280"/>
+          <a:off x="812880" y="14955480"/>
+          <a:ext cx="14173920" cy="9097920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -634,15 +817,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="20.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="26.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="32.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="29.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.84"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="1" width="11.53"/>
   </cols>
   <sheetData>
@@ -668,13 +852,10 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>8</v>
@@ -691,19 +872,16 @@
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="1" t="n">
+      <c r="G2" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>9</v>
@@ -712,87 +890,120 @@
         <v>10</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="G3" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F4" s="0"/>
+      <c r="A4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F5" s="0"/>
+      <c r="A5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F6" s="0"/>
+      <c r="E6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F7" s="0"/>
+      <c r="E7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F8" s="0"/>
+      <c r="E8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F9" s="0"/>
+      <c r="E9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F10" s="0"/>
+      <c r="E10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F11" s="0"/>
+      <c r="E11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F12" s="0"/>
+      <c r="E12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F13" s="0"/>
+      <c r="E13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F14" s="0"/>
+      <c r="E14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F15" s="0"/>
+      <c r="E15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F16" s="0"/>
+      <c r="E16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F17" s="0"/>
+      <c r="E17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F18" s="0"/>
+      <c r="E18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F19" s="0"/>
+      <c r="E19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F20" s="0"/>
+      <c r="E20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F21" s="0"/>
+      <c r="E21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F22" s="0"/>
+      <c r="E22" s="4"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A1:A1003" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D2:D100" type="list">
       <formula1>languages!$A$1:$A$26</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E2:E100" type="list">
-      <formula1>preferences!$A$1:$A$50</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -811,140 +1022,297 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="26.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="29.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="B1" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>19</v>
+        <v>33</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>21</v>
+        <v>39</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>22</v>
+        <v>42</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>23</v>
+        <v>45</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>24</v>
+        <v>48</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>25</v>
+        <v>51</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>26</v>
+        <v>54</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>27</v>
+        <v>57</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>28</v>
+        <v>60</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>29</v>
+        <v>63</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>30</v>
+        <v>66</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>31</v>
+        <v>69</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>32</v>
+        <v>72</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>33</v>
+        <v>75</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>34</v>
+        <v>78</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>35</v>
+        <v>81</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>36</v>
+        <v>84</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>37</v>
+        <v>87</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>38</v>
+        <v>90</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>39</v>
+        <v>93</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>40</v>
+        <v>96</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>41</v>
+        <v>99</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -971,7 +1339,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>11</v>
+        <v>102</v>
       </c>
       <c r="B1" s="4"/>
     </row>
@@ -995,114 +1363,114 @@
   <dimension ref="B27:L57"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="41.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="4" width="41.13"/>
   </cols>
   <sheetData>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="0" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="34" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K39" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="23.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K40" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="34" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K41" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="23.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K42" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="23.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K43" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="34" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K44" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="23.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K45" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="23.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K46" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="23.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K47" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="34" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K48" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="23.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K49" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="23.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K50" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K51" s="5" t="s">
-        <v>55</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K52" s="5" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>57</v>
+        <v>118</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K53" s="1" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="L53" s="6"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K54" s="1" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="L54" s="6"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K55" s="1" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="L55" s="6"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K56" s="1" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="L56" s="6"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K57" s="1" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="L57" s="6"/>
     </row>

--- a/tests/resources/test_data/TestCases.xlsx
+++ b/tests/resources/test_data/TestCases.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="tc" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
   <si>
     <t xml:space="preserve">*** Test Cases ***</t>
   </si>
@@ -49,7 +49,10 @@
     <t xml:space="preserve">${fixes_count}</t>
   </si>
   <si>
-    <t xml:space="preserve">Space after comma</t>
+    <t xml:space="preserve">Cz-academic Space after comma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doc1</t>
   </si>
   <si>
     <t xml:space="preserve">demo</t>
@@ -58,7 +61,37 @@
     <t xml:space="preserve">Czech (academic rules)</t>
   </si>
   <si>
-    <t xml:space="preserve">TEST_AUT_ReferenceSet_cz_ak</t>
+    <t xml:space="preserve">test-czech-academic-rules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahoj,babi, PhD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahoj, babi, PhD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cz-academic Spaces after comma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doc2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahoj,babi,znovu, PhD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahoj, babi, znovu, PhD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cz-trad Space after comma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doc3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czech (traditional rules)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test-czech-traditional-rules</t>
   </si>
   <si>
     <t xml:space="preserve">Ahoj,babi</t>
@@ -67,16 +100,16 @@
     <t xml:space="preserve">Ahoj, babi</t>
   </si>
   <si>
-    <t xml:space="preserve">Wrong format viz</t>
+    <t xml:space="preserve">Cz-trad Spaces after comma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doc4</t>
   </si>
   <si>
     <t xml:space="preserve">Ahoj,babi,znovu</t>
   </si>
   <si>
     <t xml:space="preserve">Ahoj, babi, znovu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czech (traditional rules)</t>
   </si>
   <si>
     <t xml:space="preserve">Bulgarian</t>
@@ -308,11 +341,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -339,9 +372,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>528480</xdr:colOff>
+      <xdr:colOff>528120</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>80280</xdr:rowOff>
+      <xdr:rowOff>79920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -355,7 +388,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="13993560" cy="3981600"/>
+          <a:ext cx="13993200" cy="3981240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -377,9 +410,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>679680</xdr:colOff>
+      <xdr:colOff>679320</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>5040</xdr:rowOff>
+      <xdr:rowOff>4680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -393,7 +426,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="812880" y="4551840"/>
-          <a:ext cx="4743720" cy="1142640"/>
+          <a:ext cx="4743360" cy="1142280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -415,9 +448,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>197280</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>50400</xdr:rowOff>
+      <xdr:colOff>196920</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>161280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -431,7 +464,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="812880" y="5852160"/>
-          <a:ext cx="5886720" cy="5200920"/>
+          <a:ext cx="5886360" cy="5200560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -453,9 +486,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>529920</xdr:colOff>
+      <xdr:colOff>529560</xdr:colOff>
       <xdr:row>90</xdr:row>
-      <xdr:rowOff>59760</xdr:rowOff>
+      <xdr:rowOff>59400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -468,8 +501,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="812880" y="12140640"/>
-          <a:ext cx="14807880" cy="5099040"/>
+          <a:off x="812880" y="9591120"/>
+          <a:ext cx="14807520" cy="5098680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -491,9 +524,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>709200</xdr:colOff>
+      <xdr:colOff>708840</xdr:colOff>
       <xdr:row>147</xdr:row>
-      <xdr:rowOff>157320</xdr:rowOff>
+      <xdr:rowOff>156960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -506,8 +539,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="812880" y="17505000"/>
-          <a:ext cx="14174280" cy="9098280"/>
+          <a:off x="812880" y="14955480"/>
+          <a:ext cx="14173920" cy="9097920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -634,11 +667,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="20.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="26.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="29.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="32.05"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20.76"/>
@@ -677,22 +712,22 @@
         <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="1" t="n">
         <v>1</v>
@@ -700,98 +735,201 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H3" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F4" s="0"/>
+      <c r="A4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F5" s="0"/>
+      <c r="A5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F6" s="0"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F7" s="0"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F8" s="0"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F9" s="0"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F10" s="0"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F11" s="0"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F12" s="0"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F13" s="0"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F14" s="0"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F15" s="0"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F16" s="0"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F17" s="0"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F18" s="0"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F19" s="0"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F20" s="0"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F21" s="0"/>
+      <c r="E21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F22" s="0"/>
+      <c r="E22" s="3"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E24" s="3"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E25" s="3"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E26" s="3"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E27" s="3"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E28" s="3"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E29" s="3"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E30" s="3"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E31" s="3"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E32" s="3"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E33" s="3"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E34" s="3"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E35" s="3"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E36" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A1:A1003" type="none">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A1:A1001" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D2:D100" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D2:D98" type="list">
       <formula1>languages!$A$1:$A$26</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E2:E100" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E2:E98" type="list">
       <formula1>preferences!$A$1:$A$50</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -819,132 +957,132 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -963,7 +1101,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="32.05"/>
@@ -971,9 +1109,80 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B1" s="4"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -995,114 +1204,114 @@
   <dimension ref="B27:L57"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="41.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="4" width="41.13"/>
   </cols>
   <sheetData>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="0" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="34" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K39" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="23.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K40" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="34" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K41" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="23.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K42" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="23.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K43" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="34" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K44" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="23.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K45" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="23.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K46" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="23.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K47" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="34" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K48" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="23.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K49" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="23.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K50" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K51" s="5" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K52" s="5" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K53" s="1" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="L53" s="6"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K54" s="1" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="L54" s="6"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K55" s="1" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="L55" s="6"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K56" s="1" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="L56" s="6"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K57" s="1" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="L57" s="6"/>
     </row>

--- a/tests/resources/test_data/TestCases.xlsx
+++ b/tests/resources/test_data/TestCases.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="68">
   <si>
     <t xml:space="preserve">*** Test Cases ***</t>
   </si>
@@ -37,9 +37,6 @@
     <t xml:space="preserve">${language}</t>
   </si>
   <si>
-    <t xml:space="preserve">${preference}</t>
-  </si>
-  <si>
     <t xml:space="preserve">${given}</t>
   </si>
   <si>
@@ -61,127 +58,127 @@
     <t xml:space="preserve">Czech (academic rules)</t>
   </si>
   <si>
+    <t xml:space="preserve">Ahoj,babi, PhD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahoj, babi, PhD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cz-academic Spaces after comma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doc2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahoj,babi,znovu, PhD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahoj, babi, znovu, PhD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cz-trad Space after comma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doc3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czech (traditional rules)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahoj,babi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahoj, babi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cz-trad Spaces after comma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doc4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahoj,babi,znovu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahoj, babi, znovu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulgarian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Croatian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dutch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English (UK)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English (US)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finnish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">French</t>
+  </si>
+  <si>
+    <t xml:space="preserve">German (Germany)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hungarian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Irish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latvian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lithuanian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maltese</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portuguese</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romanian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovenian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spanish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swedish</t>
+  </si>
+  <si>
     <t xml:space="preserve">test-czech-academic-rules</t>
   </si>
   <si>
-    <t xml:space="preserve">Ahoj,babi, PhD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ahoj, babi, PhD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cz-academic Spaces after comma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doc2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ahoj,babi,znovu, PhD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ahoj, babi, znovu, PhD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cz-trad Space after comma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doc3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czech (traditional rules)</t>
-  </si>
-  <si>
     <t xml:space="preserve">test-czech-traditional-rules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ahoj,babi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ahoj, babi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cz-trad Spaces after comma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doc4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ahoj,babi,znovu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ahoj, babi, znovu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulgarian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Croatian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Danish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dutch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">English (UK)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">English (US)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finnish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">French</t>
-  </si>
-  <si>
-    <t xml:space="preserve">German (Germany)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hungarian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Irish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Italian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latvian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lithuanian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maltese</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portuguese</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Romanian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slovak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slovenian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spanish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Swedish</t>
   </si>
   <si>
     <t xml:space="preserve">add test entru není exit </t>
@@ -372,9 +369,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>528120</xdr:colOff>
+      <xdr:colOff>527400</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>79920</xdr:rowOff>
+      <xdr:rowOff>79200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -388,7 +385,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="13993200" cy="3981240"/>
+          <a:ext cx="13992480" cy="3980520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -410,9 +407,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>679320</xdr:colOff>
+      <xdr:colOff>678600</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>4680</xdr:rowOff>
+      <xdr:rowOff>3960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -426,7 +423,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="812880" y="4551840"/>
-          <a:ext cx="4743360" cy="1142280"/>
+          <a:ext cx="4742640" cy="1141560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -448,9 +445,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>196920</xdr:colOff>
+      <xdr:colOff>196200</xdr:colOff>
       <xdr:row>67</xdr:row>
-      <xdr:rowOff>161280</xdr:rowOff>
+      <xdr:rowOff>160560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -464,7 +461,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="812880" y="5852160"/>
-          <a:ext cx="5886360" cy="5200560"/>
+          <a:ext cx="5885640" cy="5199840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -486,9 +483,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>529560</xdr:colOff>
+      <xdr:colOff>528840</xdr:colOff>
       <xdr:row>90</xdr:row>
-      <xdr:rowOff>59400</xdr:rowOff>
+      <xdr:rowOff>58680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -502,7 +499,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="812880" y="9591120"/>
-          <a:ext cx="14807520" cy="5098680"/>
+          <a:ext cx="14806800" cy="5097960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -524,9 +521,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>708840</xdr:colOff>
+      <xdr:colOff>708120</xdr:colOff>
       <xdr:row>147</xdr:row>
-      <xdr:rowOff>156960</xdr:rowOff>
+      <xdr:rowOff>156240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -540,7 +537,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="812880" y="14955480"/>
-          <a:ext cx="14173920" cy="9097920"/>
+          <a:ext cx="14173200" cy="9097200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -667,17 +664,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="29.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="32.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="20.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.84"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="1" width="11.53"/>
   </cols>
   <sheetData>
@@ -703,234 +699,152 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="1" t="n">
+      <c r="G2" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="1" t="n">
+      <c r="G3" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="1" t="n">
+      <c r="G4" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="1" t="n">
+      <c r="G5" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E6" s="3"/>
-      <c r="F6" s="4"/>
+      <c r="E6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E7" s="3"/>
-      <c r="F7" s="4"/>
+      <c r="E7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E8" s="3"/>
-      <c r="F8" s="4"/>
+      <c r="E8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E9" s="3"/>
-      <c r="F9" s="4"/>
+      <c r="E9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E10" s="3"/>
-      <c r="F10" s="4"/>
+      <c r="E10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E11" s="3"/>
-      <c r="F11" s="4"/>
+      <c r="E11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E12" s="3"/>
-      <c r="F12" s="4"/>
+      <c r="E12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E13" s="3"/>
-      <c r="F13" s="4"/>
+      <c r="E13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E14" s="3"/>
-      <c r="F14" s="4"/>
+      <c r="E14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E15" s="3"/>
-      <c r="F15" s="4"/>
+      <c r="E15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E16" s="3"/>
-      <c r="F16" s="4"/>
+      <c r="E16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E17" s="3"/>
-      <c r="F17" s="4"/>
+      <c r="E17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="3"/>
-      <c r="F18" s="4"/>
+      <c r="E18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="3"/>
-      <c r="F19" s="4"/>
+      <c r="E19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E20" s="3"/>
-      <c r="F20" s="4"/>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E21" s="3"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E22" s="3"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E23" s="3"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E24" s="3"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E25" s="3"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E26" s="3"/>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E27" s="3"/>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E28" s="3"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E29" s="3"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E30" s="3"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E31" s="3"/>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E32" s="3"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E33" s="3"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E34" s="3"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E35" s="3"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E36" s="3"/>
+      <c r="E20" s="4"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A1:A1001" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D2:D98" type="list">
       <formula1>languages!$A$1:$A$26</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E2:E98" type="list">
-      <formula1>preferences!$A$1:$A$50</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -957,132 +871,132 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1109,13 +1023,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1209,109 +1123,109 @@
   <sheetData>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K39" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K40" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K41" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K42" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K43" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K44" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K45" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K46" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K47" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K48" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K49" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K50" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K51" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K52" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L52" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="L52" s="6" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K53" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L53" s="6"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K54" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L54" s="6"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K55" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L55" s="6"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K56" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L56" s="6"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K57" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L57" s="6"/>
     </row>

--- a/tests/resources/test_data/TestCases.xlsx
+++ b/tests/resources/test_data/TestCases.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="tc_A2" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="tc_A3" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="tc" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="languages" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="preferences" sheetId="4" state="visible" r:id="rId6"/>
@@ -16,7 +16,7 @@
     <sheet name="_pattern" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">tc_A2!$A$1:$G$7</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">tc_A3!$A$1:$G$7</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="80">
   <si>
     <t xml:space="preserve">*** Test Cases ***</t>
   </si>
@@ -51,7 +51,7 @@
     <t xml:space="preserve">${fixes_count}</t>
   </si>
   <si>
-    <t xml:space="preserve">44. Guns N’ Roses</t>
+    <t xml:space="preserve">44. Guns N’ Roses [Czech (academic rules)]</t>
   </si>
   <si>
     <t xml:space="preserve">Czech (academic rules)</t>
@@ -67,10 +67,13 @@
 Guns N’ Roses</t>
   </si>
   <si>
+    <t xml:space="preserve">44. Guns N’ Roses [Czech (traditional rules)]</t>
+  </si>
+  <si>
     <t xml:space="preserve">Czech (traditional rules)</t>
   </si>
   <si>
-    <t xml:space="preserve">45. Correct form of C. a K. in Czech</t>
+    <t xml:space="preserve">45. Correct form of C. a K. in Czech [Czech (academic rules)]</t>
   </si>
   <si>
     <t xml:space="preserve">C.a k.
@@ -81,7 +84,10 @@
 C.&amp;nbsp;a&amp;nbsp;k.</t>
   </si>
   <si>
-    <t xml:space="preserve">66. Correct form of et al.</t>
+    <t xml:space="preserve">45. Correct form of C. a K. in Czech [Czech (traditional rules)]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66. Correct form of et al. [Czech (academic rules)]</t>
   </si>
   <si>
     <t xml:space="preserve">Author et all
@@ -92,6 +98,9 @@
     <t xml:space="preserve">Author et&amp;nbsp;al.
 Author et&amp;nbsp;al.
 Author et&amp;nbsp;al.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66. Correct form of et al. [Czech (traditional rules)]</t>
   </si>
   <si>
     <t xml:space="preserve">Cz-academic Space after comma</t>
@@ -359,7 +368,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -374,10 +383,6 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -527,13 +532,13 @@
   <dimension ref="A1:G1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="29.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="43.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="60.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="90.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="29.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="20.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.84"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -571,21 +576,21 @@
       <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="3" t="s">
@@ -595,7 +600,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -603,61 +608,61 @@
         <v>8</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="F5" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="G5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>16</v>
+      <c r="E6" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>17</v>
+      <c r="F7" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="G7" s="3"/>
     </row>
@@ -9139,60 +9144,12 @@
       <c r="F949" s="3"/>
       <c r="G949" s="3"/>
     </row>
-    <row r="950" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A950" s="3"/>
-      <c r="B950" s="3"/>
-      <c r="C950" s="3"/>
-      <c r="D950" s="3"/>
-      <c r="E950" s="3"/>
-      <c r="F950" s="3"/>
-      <c r="G950" s="3"/>
-    </row>
-    <row r="951" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A951" s="3"/>
-      <c r="B951" s="3"/>
-      <c r="C951" s="3"/>
-      <c r="D951" s="3"/>
-      <c r="E951" s="3"/>
-      <c r="F951" s="3"/>
-      <c r="G951" s="3"/>
-    </row>
-    <row r="952" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A952" s="3"/>
-      <c r="B952" s="3"/>
-      <c r="C952" s="3"/>
-      <c r="D952" s="3"/>
-      <c r="E952" s="3"/>
-      <c r="F952" s="3"/>
-      <c r="G952" s="3"/>
-    </row>
-    <row r="953" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A953" s="3"/>
-      <c r="B953" s="3"/>
-      <c r="C953" s="3"/>
-      <c r="D953" s="3"/>
-      <c r="E953" s="3"/>
-      <c r="F953" s="3"/>
-      <c r="G953" s="3"/>
-    </row>
-    <row r="954" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A954" s="3"/>
-      <c r="B954" s="3"/>
-      <c r="C954" s="3"/>
-      <c r="D954" s="3"/>
-      <c r="E954" s="3"/>
-      <c r="F954" s="3"/>
-      <c r="G954" s="3"/>
-    </row>
-    <row r="955" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A955" s="3"/>
-      <c r="B955" s="3"/>
-      <c r="C955" s="3"/>
-      <c r="D955" s="3"/>
-      <c r="E955" s="3"/>
-      <c r="F955" s="3"/>
-      <c r="G955" s="3"/>
-    </row>
+    <row r="1048525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -9295,22 +9252,22 @@
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>1</v>
@@ -9318,22 +9275,22 @@
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>2</v>
@@ -9341,22 +9298,22 @@
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>1</v>
@@ -9364,22 +9321,22 @@
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>2</v>
@@ -9439,127 +9396,127 @@
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -9586,13 +9543,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9686,111 +9643,111 @@
   <sheetData>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K39" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K40" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K41" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K42" s="5" t="s">
+    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K39" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K43" s="5" t="s">
+    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K40" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K44" s="5" t="s">
+    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K41" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K45" s="5" t="s">
+    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K42" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K46" s="5" t="s">
+    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K43" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K47" s="5" t="s">
+    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K44" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K48" s="5" t="s">
+    <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K45" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K49" s="5" t="s">
+    <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K46" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K50" s="5" t="s">
+    <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K47" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K51" s="5" t="s">
+    <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K48" s="4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K52" s="5" t="s">
+    <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K49" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="L52" s="6" t="s">
+    </row>
+    <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K50" s="4" t="s">
         <v>76</v>
       </c>
     </row>
+    <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K51" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K52" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="L52" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K53" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
-      <c r="L53" s="6"/>
+      <c r="L53" s="5"/>
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K54" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
-      <c r="L54" s="6"/>
+      <c r="L54" s="5"/>
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K55" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
-      <c r="L55" s="6"/>
+      <c r="L55" s="5"/>
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K56" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
-      <c r="L56" s="6"/>
+      <c r="L56" s="5"/>
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K57" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
-      <c r="L57" s="6"/>
+      <c r="L57" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/tests/resources/test_data/TestCases.xlsx
+++ b/tests/resources/test_data/TestCases.xlsx
@@ -399,7 +399,9 @@
 Guns N’ Roses</t>
         </is>
       </c>
-      <c r="G2" s="9" t="n"/>
+      <c r="G2" s="9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" ht="12.75" customHeight="1" s="7">
       <c r="A3" s="9" t="inlineStr">
@@ -428,7 +430,9 @@
 Guns N’ Roses</t>
         </is>
       </c>
-      <c r="G3" s="9" t="n"/>
+      <c r="G3" s="9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" ht="12.75" customHeight="1" s="7">
       <c r="A4" s="9" t="inlineStr">
@@ -455,7 +459,9 @@
 C.&amp;nbsp;a&amp;nbsp;k.</t>
         </is>
       </c>
-      <c r="G4" s="9" t="n"/>
+      <c r="G4" s="9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" ht="12.75" customHeight="1" s="7">
       <c r="A5" s="9" t="inlineStr">
@@ -482,7 +488,9 @@
 C.&amp;nbsp;a&amp;nbsp;k.</t>
         </is>
       </c>
-      <c r="G5" s="9" t="n"/>
+      <c r="G5" s="9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" ht="12.75" customHeight="1" s="7">
       <c r="A6" s="9" t="inlineStr">
@@ -512,7 +520,7 @@
         </is>
       </c>
       <c r="G6" s="9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1" s="7">
@@ -542,7 +550,9 @@
 Author et&amp;nbsp;al.</t>
         </is>
       </c>
-      <c r="G7" s="9" t="n"/>
+      <c r="G7" s="9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" ht="12.75" customHeight="1" s="7">
       <c r="A8" s="9" t="n"/>

--- a/tests/resources/test_data/TestCases.xlsx
+++ b/tests/resources/test_data/TestCases.xlsx
@@ -8,8 +8,8 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="tc_A3" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="tc_final" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="tc_final" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="tc_A3" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="tc" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="languages" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="preferences" sheetId="5" state="visible" r:id="rId7"/>
@@ -17,8 +17,8 @@
     <sheet name="_pattern" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">tc_A3!$A$1:$G$7</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">tc_final!$A$1:$G$7</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">tc_A3!$A$1:$G$7</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">tc_final!$A$1:$G$7</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -53,21 +53,10 @@
     <t xml:space="preserve">${fixes_count}</t>
   </si>
   <si>
-    <t xml:space="preserve">45. Correct form of C. a K. in Czech [Czech (academic rules)]</t>
+    <t xml:space="preserve">44. Guns N’ Roses [Czech (academic rules)]</t>
   </si>
   <si>
     <t xml:space="preserve">Czech (academic rules)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C.a k.
-C. a k.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C.&amp;nbsp;a&amp;nbsp;k.
-C.&amp;nbsp;a&amp;nbsp;k.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44. Guns N’ Roses [Czech (academic rules)]</t>
   </si>
   <si>
     <t xml:space="preserve">Guns’N’Roses
@@ -84,6 +73,17 @@
   </si>
   <si>
     <t xml:space="preserve">Czech (traditional rules)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45. Correct form of C. a K. in Czech [Czech (academic rules)]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.a k.
+C. a k.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.&amp;nbsp;a&amp;nbsp;k.
+C.&amp;nbsp;a&amp;nbsp;k.</t>
   </si>
   <si>
     <t xml:space="preserve">45. Correct form of C. a K. in Czech [Czech (traditional rules)]</t>
@@ -377,7 +377,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -395,11 +395,15 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -653,7 +657,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="58.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -665,57 +669,107 @@
       <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="78.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="3" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-    </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3"/>
+      <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="D5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3"/>
+      <c r="A6" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3"/>
+      <c r="A7" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3"/>
@@ -9200,7 +9254,7 @@
   <autoFilter ref="A1:G7"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -9249,9 +9303,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="58.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -9259,109 +9313,59 @@
         <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>13</v>
+      <c r="F2" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="78.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>14</v>
-      </c>
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
-      <c r="D6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>3</v>
-      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
-      <c r="D7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>3</v>
-      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3"/>
@@ -17846,7 +17850,7 @@
   <autoFilter ref="A1:G7"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -17953,7 +17957,7 @@
         <v>23</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>32</v>
@@ -17976,7 +17980,7 @@
         <v>23</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>36</v>
@@ -18042,7 +18046,7 @@
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18293,75 +18297,75 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K39" s="6" t="s">
+      <c r="K39" s="7" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K40" s="6" t="s">
+      <c r="K40" s="7" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K41" s="6" t="s">
+      <c r="K41" s="7" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K42" s="6" t="s">
+      <c r="K42" s="7" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K43" s="6" t="s">
+      <c r="K43" s="7" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K44" s="6" t="s">
+      <c r="K44" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K45" s="6" t="s">
+      <c r="K45" s="7" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K46" s="6" t="s">
+      <c r="K46" s="7" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K47" s="6" t="s">
+      <c r="K47" s="7" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K48" s="6" t="s">
+      <c r="K48" s="7" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K49" s="6" t="s">
+      <c r="K49" s="7" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K50" s="6" t="s">
+      <c r="K50" s="7" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K51" s="6" t="s">
+      <c r="K51" s="7" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="K52" s="6" t="s">
+      <c r="K52" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="L52" s="7" t="s">
+      <c r="L52" s="8" t="s">
         <v>79</v>
       </c>
     </row>
@@ -18369,31 +18373,31 @@
       <c r="K53" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="L53" s="7"/>
+      <c r="L53" s="8"/>
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K54" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="L54" s="7"/>
+      <c r="L54" s="8"/>
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K55" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="L55" s="7"/>
+      <c r="L55" s="8"/>
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K56" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="L56" s="7"/>
+      <c r="L56" s="8"/>
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K57" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="L57" s="7"/>
+      <c r="L57" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/tests/resources/test_data/TestCases.xlsx
+++ b/tests/resources/test_data/TestCases.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="209">
   <si>
     <t xml:space="preserve">*** Test Cases ***</t>
   </si>
@@ -99,9 +99,6 @@
   </si>
   <si>
     <t xml:space="preserve">45__Correct_form_of_C__a_K__in_CzechCzech__traditional_rules_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ddddd</t>
   </si>
   <si>
     <t xml:space="preserve">41__rock__n__rollEnglish</t>
@@ -1163,9 +1160,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -9699,86 +9694,86 @@
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="G2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="G3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="G5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="G6" s="4"/>
     </row>
@@ -9795,7 +9790,7 @@
         <v>12</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G7" s="4"/>
     </row>
@@ -9812,92 +9807,92 @@
         <v>12</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G13" s="4"/>
     </row>
@@ -9937,29 +9932,29 @@
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="F16" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="G16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
@@ -9967,12 +9962,12 @@
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -9980,12 +9975,12 @@
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
@@ -9993,12 +9988,12 @@
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
@@ -10006,12 +10001,12 @@
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
@@ -10019,12 +10014,12 @@
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
@@ -10032,194 +10027,194 @@
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="F23" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>53</v>
       </c>
       <c r="G23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E24" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>56</v>
       </c>
       <c r="G24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E25" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="G25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E26" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>62</v>
       </c>
       <c r="G26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="F27" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="G27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="F28" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>70</v>
       </c>
       <c r="G28" s="4"/>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E29" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="G29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
       <c r="D30" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E30" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>76</v>
       </c>
       <c r="G30" s="4"/>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E31" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>79</v>
       </c>
       <c r="G31" s="4"/>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E32" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>82</v>
       </c>
       <c r="G32" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="F33" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>86</v>
       </c>
       <c r="G33" s="4"/>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -10227,16 +10222,16 @@
         <v>11</v>
       </c>
       <c r="E34" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="G34" s="4"/>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -10244,55 +10239,55 @@
         <v>15</v>
       </c>
       <c r="E35" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F35" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>89</v>
       </c>
       <c r="G35" s="4"/>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E36" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F36" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="G36" s="4"/>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E37" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="G37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
       <c r="D38" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
@@ -10300,12 +10295,12 @@
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
@@ -10313,12 +10308,12 @@
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
@@ -10326,12 +10321,12 @@
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
@@ -10339,7 +10334,7 @@
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -10352,7 +10347,7 @@
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -10365,7 +10360,7 @@
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -10378,7 +10373,7 @@
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -10391,12 +10386,12 @@
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
@@ -10404,7 +10399,7 @@
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -10417,7 +10412,7 @@
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -10430,12 +10425,12 @@
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
@@ -10443,7 +10438,7 @@
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -10456,7 +10451,7 @@
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -10469,12 +10464,12 @@
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
       <c r="D52" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
@@ -10482,12 +10477,12 @@
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
       <c r="D53" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
@@ -19087,92 +19082,92 @@
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="G2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="G3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="G5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="G6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -19183,13 +19178,13 @@
         <v>12</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -19200,98 +19195,98 @@
         <v>12</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -19308,7 +19303,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -19325,29 +19320,29 @@
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="F16" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="G16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
@@ -19355,12 +19350,12 @@
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -19368,12 +19363,12 @@
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
@@ -19381,12 +19376,12 @@
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
@@ -19394,12 +19389,12 @@
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
@@ -19407,12 +19402,12 @@
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
@@ -19420,194 +19415,194 @@
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="F23" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>53</v>
       </c>
       <c r="G23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E24" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>56</v>
       </c>
       <c r="G24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E25" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="G25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E26" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>62</v>
       </c>
       <c r="G26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="F27" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="G27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="F28" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>70</v>
       </c>
       <c r="G28" s="4"/>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E29" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="G29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
       <c r="D30" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E30" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>76</v>
       </c>
       <c r="G30" s="4"/>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E31" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>79</v>
       </c>
       <c r="G31" s="4"/>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E32" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>82</v>
       </c>
       <c r="G32" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="F33" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>86</v>
       </c>
       <c r="G33" s="4"/>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -19615,16 +19610,16 @@
         <v>11</v>
       </c>
       <c r="E34" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="G34" s="4"/>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -19632,55 +19627,55 @@
         <v>15</v>
       </c>
       <c r="E35" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F35" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>89</v>
       </c>
       <c r="G35" s="4"/>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E36" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F36" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>89</v>
       </c>
       <c r="G36" s="4"/>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E37" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="G37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
       <c r="D38" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
@@ -19688,12 +19683,12 @@
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
@@ -19701,12 +19696,12 @@
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
@@ -19714,12 +19709,12 @@
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
@@ -19727,7 +19722,7 @@
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -19740,7 +19735,7 @@
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -19753,7 +19748,7 @@
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -19766,7 +19761,7 @@
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -19779,12 +19774,12 @@
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
@@ -19792,7 +19787,7 @@
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -19805,7 +19800,7 @@
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -19818,12 +19813,12 @@
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
@@ -19831,7 +19826,7 @@
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -19844,7 +19839,7 @@
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -19857,12 +19852,12 @@
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
       <c r="D52" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
@@ -19870,12 +19865,12 @@
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
       <c r="D53" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
@@ -28466,7 +28461,7 @@
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -37063,22 +37058,22 @@
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>165</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>166</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>168</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>1</v>
@@ -37086,22 +37081,22 @@
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>170</v>
-      </c>
       <c r="C3" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>171</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>172</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>2</v>
@@ -37109,22 +37104,22 @@
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>174</v>
-      </c>
       <c r="C4" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>175</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>176</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>1</v>
@@ -37132,22 +37127,22 @@
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>178</v>
-      </c>
       <c r="C5" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>179</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>180</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>2</v>
@@ -37212,122 +37207,122 @@
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -37354,13 +37349,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -37454,109 +37449,109 @@
   <sheetData>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K39" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K40" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K41" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K42" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K43" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K44" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K45" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K46" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K47" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K48" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K49" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K50" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K51" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K52" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="L52" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="L52" s="9" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K53" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L53" s="9"/>
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K54" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L54" s="9"/>
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K55" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L55" s="9"/>
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K56" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L56" s="9"/>
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K57" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L57" s="9"/>
     </row>

--- a/tests/resources/test_data/TestCases.xlsx
+++ b/tests/resources/test_data/TestCases.xlsx
@@ -468,7 +468,7 @@
       <c r="J2" s="10" t="inlineStr"/>
       <c r="K2" s="10" t="inlineStr">
         <is>
-          <t>2026-05-19T18:15:44.058208</t>
+          <t>2026-05-20T03:01:32.307911</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       <c r="J3" s="10" t="inlineStr"/>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <t>2026-05-19T18:15:51.836175</t>
+          <t>2026-05-20T03:01:41.985314</t>
         </is>
       </c>
     </row>
@@ -549,12 +549,12 @@
       </c>
       <c r="J4" s="10" t="inlineStr">
         <is>
-          <t>The text of element  should have been 'C.&amp;nbsp;a&amp;nbsp;k. C.&amp;nbsp;a&amp;nbsp;k.' but it was 'C.a k. C. a k.'.</t>
+          <t>The text of element  should have been 'C.&amp;nbsp;a&amp;nbsp;k.C.&amp;nbsp;a&amp;nbsp;k.' but it was 'C.a k.C. a k.'.</t>
         </is>
       </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
-          <t>2026-05-19T18:15:58.947816</t>
+          <t>2026-05-20T03:01:53.844638</t>
         </is>
       </c>
     </row>
@@ -593,12 +593,12 @@
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>The text of element  should have been 'C.&amp;nbsp;a&amp;nbsp;k. C.&amp;nbsp;a&amp;nbsp;k.' but it was 'C.a k. C. a k.'.</t>
+          <t>The text of element  should have been 'C.&amp;nbsp;a&amp;nbsp;k.C.&amp;nbsp;a&amp;nbsp;k.' but it was 'C.a k.C. a k.'.</t>
         </is>
       </c>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>2026-05-19T18:16:05.425344</t>
+          <t>2026-05-20T03:01:58.883678</t>
         </is>
       </c>
     </row>

--- a/tests/resources/test_data/TestCases.xlsx
+++ b/tests/resources/test_data/TestCases.xlsx
@@ -468,7 +468,7 @@
       <c r="J2" s="10" t="inlineStr"/>
       <c r="K2" s="10" t="inlineStr">
         <is>
-          <t>2026-05-20T03:01:32.307911</t>
+          <t>2026-05-20T03:10:52.686455</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       <c r="J3" s="10" t="inlineStr"/>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <t>2026-05-20T03:01:41.985314</t>
+          <t>2026-05-20T03:11:01.560806</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
-          <t>2026-05-20T03:01:53.844638</t>
+          <t>2026-05-20T03:11:14.709599</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>2026-05-20T03:01:58.883678</t>
+          <t>2026-05-20T03:11:25.879240</t>
         </is>
       </c>
     </row>

--- a/tests/resources/test_data/TestCases.xlsx
+++ b/tests/resources/test_data/TestCases.xlsx
@@ -132,14 +132,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
@@ -163,14 +163,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
@@ -461,14 +461,14 @@
           <t>Czech (academic rules)</t>
         </is>
       </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>Guns’N’Roses
 Guns n'Roses
 Guns ‘N’ Roses</t>
         </is>
       </c>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="F2" s="17" t="inlineStr">
         <is>
           <t>Guns N’ Roses
 Guns n’Roses
@@ -489,12 +489,11 @@
           <t>2026-05-20T03:10:52.686455</t>
         </is>
       </c>
-      <c r="L2" s="17" t="n"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>C:\Users\ocape\IdeaProjects\TypofixAppTest\tests\resources\selenium-element-screenshot-9.png</t>
-        </is>
-      </c>
+      <c r="L2" s="18">
+        <f>HYPERLINK("C:\Users\ocape\IdeaProjects\TypofixAppTest\results\selenium-element-screenshot-9.png", "LINK")</f>
+        <v/>
+      </c>
+      <c r="M2" s="11" t="n"/>
     </row>
     <row r="3" ht="78" customHeight="1" s="12">
       <c r="A3" s="15" t="inlineStr">
@@ -509,14 +508,14 @@
           <t>Czech (traditional rules)</t>
         </is>
       </c>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>Guns’N’Roses
 Guns n'Roses
 Guns ‘N’ Roses</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>Guns N’ Roses
 Guns n’Roses
@@ -537,12 +536,11 @@
           <t>2026-05-20T03:11:01.560806</t>
         </is>
       </c>
-      <c r="L3" s="11" t="n"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>C:\Users\ocape\IdeaProjects\TypofixAppTest\tests\resources\selenium-element-screenshot-10.png</t>
-        </is>
-      </c>
+      <c r="L3" s="11">
+        <f>HYPERLINK("C:\Users\ocape\IdeaProjects\TypofixAppTest\results\selenium-element-screenshot-10.png", "LINK")</f>
+        <v/>
+      </c>
+      <c r="M3" s="11" t="n"/>
     </row>
     <row r="4" ht="12.75" customHeight="1" s="12">
       <c r="A4" s="15" t="inlineStr">
@@ -557,13 +555,13 @@
           <t>Czech (academic rules)</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>C.a k.
 C. a k.</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>C.&amp;nbsp;a&amp;nbsp;k.
 C.&amp;nbsp;a&amp;nbsp;k.</t>
@@ -587,12 +585,11 @@
           <t>2026-05-20T03:11:14.709599</t>
         </is>
       </c>
-      <c r="L4" s="11" t="n"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>C:\Users\ocape\IdeaProjects\TypofixAppTest\tests\resources\selenium-element-screenshot-11.png</t>
-        </is>
-      </c>
+      <c r="L4" s="11">
+        <f>HYPERLINK("C:\Users\ocape\IdeaProjects\TypofixAppTest\results\selenium-element-screenshot-11.png", "LINK")</f>
+        <v/>
+      </c>
+      <c r="M4" s="11" t="n"/>
     </row>
     <row r="5" ht="12.75" customHeight="1" s="12">
       <c r="A5" s="15" t="inlineStr">
@@ -607,13 +604,13 @@
           <t>Czech (traditional rules)</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>C.a k.
 C. a k.</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>C.&amp;nbsp;a&amp;nbsp;k.
 C.&amp;nbsp;a&amp;nbsp;k.</t>
@@ -637,12 +634,11 @@
           <t>2026-05-20T03:11:25.879240</t>
         </is>
       </c>
-      <c r="L5" s="11" t="n"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>C:\Users\ocape\IdeaProjects\TypofixAppTest\tests\resources\selenium-element-screenshot-12.png</t>
-        </is>
-      </c>
+      <c r="L5" s="11">
+        <f>HYPERLINK("C:\Users\ocape\IdeaProjects\TypofixAppTest\results\selenium-element-screenshot-12.png", "LINK")</f>
+        <v/>
+      </c>
+      <c r="M5" s="11" t="n"/>
     </row>
     <row r="6" ht="12.75" customHeight="1" s="12">
       <c r="A6" s="15" t="n"/>
@@ -9199,14 +9195,14 @@
           <t>English</t>
         </is>
       </c>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>rock‘n’roll
 rock' n' roll
 rock’n’roll</t>
         </is>
       </c>
-      <c r="F2" s="18" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>rock ’n’ roll
 rock ’n’ roll
@@ -9228,7 +9224,7 @@
           <t>English (UK)</t>
         </is>
       </c>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>rock‘n’roll
 rock' n' roll
@@ -9264,7 +9260,7 @@
 rock’n’roll</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>rock ’n’ roll
 rock ’n’ roll
@@ -9286,14 +9282,14 @@
           <t>German (Germany)</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>rock‘n’roll
 rock' n' roll
 rock’n’roll</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>rock ’n’ roll
 rock ’n’ roll
@@ -9315,14 +9311,14 @@
           <t>Spanish</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>rock‘n’roll
 rock' n' roll
 rock’n’roll</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>rock ’n’ roll
 rock ’n’ roll
@@ -9344,14 +9340,14 @@
           <t>Czech (academic rules)</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>Guns’N’Roses
 Guns n'Roses
 Guns ‘N’ Roses</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>Guns N’ Roses
 Guns N’ Roses
@@ -9373,14 +9369,14 @@
           <t>Czech (traditional rules)</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>Guns’N’Roses
 Guns n'Roses
 Guns ‘N’ Roses</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Guns N’ Roses
 Guns N’ Roses
@@ -9402,14 +9398,14 @@
           <t>English</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>Guns’N’Roses
 Guns n'Roses
 Guns ‘N’ Roses</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>Guns N’ Roses
 Guns N’ Roses
@@ -9431,14 +9427,14 @@
           <t>English (UK)</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>Guns’N’Roses
 Guns n'Roses
 Guns ‘N’ Roses</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>Guns N’ Roses
 Guns N’ Roses
@@ -9460,14 +9456,14 @@
           <t>English (US)</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>Guns’N’Roses
 Guns n'Roses
 Guns ‘N’ Roses</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>Guns N’ Roses
 Guns N’ Roses
@@ -9489,14 +9485,14 @@
           <t>German (Germany)</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>Guns’N’Roses
 Guns n'Roses
 Guns ‘N’ Roses</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>Guns N’ Roses
 Guns N’ Roses
@@ -9518,14 +9514,14 @@
           <t>Spanish</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>Guns’N’Roses
 Guns n'Roses
 Guns ‘N’ Roses</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>Guns N’ Roses
 Guns N’ Roses
@@ -9547,13 +9543,13 @@
           <t>Czech (academic rules)</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>C.a k.
 C. a k.</t>
         </is>
       </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>C.&amp;nbsp;a&amp;nbsp;k.
 C.&amp;nbsp;a&amp;nbsp;k.</t>
@@ -9574,13 +9570,13 @@
           <t>Czech (traditional rules)</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>C.a k.
 C. a k.</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>C.&amp;nbsp;a&amp;nbsp;k.
 C.&amp;nbsp;a&amp;nbsp;k.</t>
@@ -9601,14 +9597,14 @@
           <t>Italian</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>E' (Italian)
 E’ (Italian)
 E` (Italian)</t>
         </is>
       </c>
-      <c r="F16" s="15" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>È (Italian)
 È (Italian)
@@ -9863,7 +9859,7 @@
 lij́n (Dutch)</t>
         </is>
       </c>
-      <c r="F28" s="18" t="inlineStr">
+      <c r="F28" s="16" t="inlineStr">
         <is>
           <t>líȷ́n (Dutch)
 líȷ́n (Dutch)</t>
@@ -10009,14 +10005,14 @@
           <t>Czech (academic rules)</t>
         </is>
       </c>
-      <c r="E34" s="18" t="inlineStr">
+      <c r="E34" s="16" t="inlineStr">
         <is>
           <t>Author et all
 Author et al
 Author et all.</t>
         </is>
       </c>
-      <c r="F34" s="18" t="inlineStr">
+      <c r="F34" s="16" t="inlineStr">
         <is>
           <t>Author et&amp;nbsp;al.
 Author et&amp;nbsp;al.
@@ -10038,14 +10034,14 @@
           <t>Czech (traditional rules)</t>
         </is>
       </c>
-      <c r="E35" s="18" t="inlineStr">
+      <c r="E35" s="16" t="inlineStr">
         <is>
           <t>Author et all
 Author et al
 Author et all.</t>
         </is>
       </c>
-      <c r="F35" s="18" t="inlineStr">
+      <c r="F35" s="16" t="inlineStr">
         <is>
           <t>Author et&amp;nbsp;al.
 Author et&amp;nbsp;al.
@@ -10067,14 +10063,14 @@
           <t>English (UK)</t>
         </is>
       </c>
-      <c r="E36" s="18" t="inlineStr">
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t>Author et all
 Author et al
 Author et all.</t>
         </is>
       </c>
-      <c r="F36" s="18" t="inlineStr">
+      <c r="F36" s="16" t="inlineStr">
         <is>
           <t>Author et&amp;nbsp;al.
 Author et&amp;nbsp;al.
@@ -10096,14 +10092,14 @@
           <t>English (US)</t>
         </is>
       </c>
-      <c r="E37" s="15" t="inlineStr">
+      <c r="E37" s="16" t="inlineStr">
         <is>
           <t>Author et all
 Author et al
 Author et all.</t>
         </is>
       </c>
-      <c r="F37" s="18" t="inlineStr">
+      <c r="F37" s="16" t="inlineStr">
         <is>
           <t>Author et&amp;nbsp;al.
 Author et&amp;nbsp;al.
@@ -18999,7 +18995,7 @@
           <t>English</t>
         </is>
       </c>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>rock‘n’roll
 rock' n' roll
@@ -19028,14 +19024,14 @@
           <t>English (UK)</t>
         </is>
       </c>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>rock‘n’roll
 rock' n' roll
 rock’n’roll</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>rock ’n’ roll
 rock ’n’ roll
@@ -19057,14 +19053,14 @@
           <t>English (US)</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>rock‘n’roll
 rock' n' roll
 rock’n’roll</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>rock ’n’ roll
 rock ’n’ roll
@@ -19086,7 +19082,7 @@
           <t>German (Germany)</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>rock‘n’roll
 rock' n' roll
@@ -19115,7 +19111,7 @@
           <t>Spanish</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>rock‘n’roll
 rock' n' roll
@@ -19144,14 +19140,14 @@
           <t>Czech (academic rules)</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>Guns’N’Roses
 Guns n'Roses
 Guns ‘N’ Roses</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>Guns N’ Roses
 Guns N’ Roses
@@ -19173,14 +19169,14 @@
           <t>Czech (traditional rules)</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>Guns’N’Roses
 Guns n'Roses
 Guns ‘N’ Roses</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Guns N’ Roses
 Guns N’ Roses
@@ -19202,7 +19198,7 @@
           <t>English</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>Guns’N’Roses
 Guns n'Roses
@@ -19231,14 +19227,14 @@
           <t>English (UK)</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>Guns’N’Roses
 Guns n'Roses
 Guns ‘N’ Roses</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>Guns N’ Roses
 Guns N’ Roses
@@ -19260,14 +19256,14 @@
           <t>English (US)</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>Guns’N’Roses
 Guns n'Roses
 Guns ‘N’ Roses</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>Guns N’ Roses
 Guns N’ Roses
@@ -19289,14 +19285,14 @@
           <t>German (Germany)</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>Guns’N’Roses
 Guns n'Roses
 Guns ‘N’ Roses</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>Guns N’ Roses
 Guns N’ Roses
@@ -19318,14 +19314,14 @@
           <t>Spanish</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>Guns’N’Roses
 Guns n'Roses
 Guns ‘N’ Roses</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>Guns N’ Roses
 Guns N’ Roses
@@ -19347,13 +19343,13 @@
           <t>Czech (academic rules)</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>C.a k.
 C. a k.</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>C.&amp;nbsp;a&amp;nbsp;k.
 C.&amp;nbsp;a&amp;nbsp;k.</t>
@@ -19374,13 +19370,13 @@
           <t>Czech (traditional rules)</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>C.a k.
 C. a k.</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>C.&amp;nbsp;a&amp;nbsp;k.
 C.&amp;nbsp;a&amp;nbsp;k.</t>
@@ -19401,14 +19397,14 @@
           <t>Italian</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>E' (Italian)
 E’ (Italian)
 E` (Italian)</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>È (Italian)
 È (Italian)
@@ -19657,13 +19653,13 @@
           <t>Dutch</t>
         </is>
       </c>
-      <c r="E28" s="18" t="inlineStr">
+      <c r="E28" s="16" t="inlineStr">
         <is>
           <t>liȷ́n (Dutch)
 lij́n (Dutch)</t>
         </is>
       </c>
-      <c r="F28" s="18" t="inlineStr">
+      <c r="F28" s="16" t="inlineStr">
         <is>
           <t>líȷ́n (Dutch)
 líȷ́n (Dutch)</t>
@@ -19809,14 +19805,14 @@
           <t>Czech (academic rules)</t>
         </is>
       </c>
-      <c r="E34" s="18" t="inlineStr">
+      <c r="E34" s="16" t="inlineStr">
         <is>
           <t>Author et all
 Author et al
 Author et all.</t>
         </is>
       </c>
-      <c r="F34" s="18" t="inlineStr">
+      <c r="F34" s="16" t="inlineStr">
         <is>
           <t>Author et&amp;nbsp;al.
 Author et&amp;nbsp;al.
@@ -19838,14 +19834,14 @@
           <t>Czech (traditional rules)</t>
         </is>
       </c>
-      <c r="E35" s="18" t="inlineStr">
+      <c r="E35" s="16" t="inlineStr">
         <is>
           <t>Author et all
 Author et al
 Author et all.</t>
         </is>
       </c>
-      <c r="F35" s="18" t="inlineStr">
+      <c r="F35" s="16" t="inlineStr">
         <is>
           <t>Author et&amp;nbsp;al.
 Author et&amp;nbsp;al.
@@ -19867,14 +19863,14 @@
           <t>English (UK)</t>
         </is>
       </c>
-      <c r="E36" s="18" t="inlineStr">
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t>Author et all
 Author et al
 Author et all.</t>
         </is>
       </c>
-      <c r="F36" s="18" t="inlineStr">
+      <c r="F36" s="16" t="inlineStr">
         <is>
           <t>Author et&amp;nbsp;al.
 Author et&amp;nbsp;al.
@@ -19896,14 +19892,14 @@
           <t>English (US)</t>
         </is>
       </c>
-      <c r="E37" s="18" t="inlineStr">
+      <c r="E37" s="16" t="inlineStr">
         <is>
           <t>Author et all
 Author et al
 Author et all.</t>
         </is>
       </c>
-      <c r="F37" s="18" t="inlineStr">
+      <c r="F37" s="16" t="inlineStr">
         <is>
           <t>Author et&amp;nbsp;al.
 Author et&amp;nbsp;al.
@@ -28791,13 +28787,13 @@
           <t>Czech (academic rules)</t>
         </is>
       </c>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>C.a k.
 C. a k.</t>
         </is>
       </c>
-      <c r="F2" s="18" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>C.&amp;nbsp;a&amp;nbsp;k.
 C.&amp;nbsp;a&amp;nbsp;k.</t>

--- a/tests/resources/test_data/TestCases.xlsx
+++ b/tests/resources/test_data/TestCases.xlsx
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="L2" s="18">
-        <f>HYPERLINK("C:\Users\ocape\IdeaProjects\TypofixAppTest\results\selenium-element-screenshot-9.png", "LINK")</f>
+        <f>HYPERLINK("C:\Users\ocape\IdeaProjects\TypofixAppTest\tests\resources\test_data\pcx_dir\44__Guns_N__RosesCzech__academic_rules_2026_05_20T03_10_52_686455.png", "LINK")</f>
         <v/>
       </c>
       <c r="M2" s="11" t="n"/>
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="L3" s="11">
-        <f>HYPERLINK("C:\Users\ocape\IdeaProjects\TypofixAppTest\results\selenium-element-screenshot-10.png", "LINK")</f>
+        <f>HYPERLINK("C:\Users\ocape\IdeaProjects\TypofixAppTest\tests\resources\test_data\pcx_dir\44__Guns_N__RosesCzech__traditional_rules_2026_05_20T03_11_01_560806.png", "LINK")</f>
         <v/>
       </c>
       <c r="M3" s="11" t="n"/>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="L4" s="11">
-        <f>HYPERLINK("C:\Users\ocape\IdeaProjects\TypofixAppTest\results\selenium-element-screenshot-11.png", "LINK")</f>
+        <f>HYPERLINK("C:\Users\ocape\IdeaProjects\TypofixAppTest\tests\resources\test_data\pcx_dir\45__Correct_form_of_C__a_K__in_CzechCzech__academic_rules_2026_05_20T03_11_14_709599.png", "LINK")</f>
         <v/>
       </c>
       <c r="M4" s="11" t="n"/>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="L5" s="11">
-        <f>HYPERLINK("C:\Users\ocape\IdeaProjects\TypofixAppTest\results\selenium-element-screenshot-12.png", "LINK")</f>
+        <f>HYPERLINK("C:\Users\ocape\IdeaProjects\TypofixAppTest\tests\resources\test_data\pcx_dir\45__Correct_form_of_C__a_K__in_CzechCzech__traditional_rules_2026_05_20T03_11_25_879240.png", "LINK")</f>
         <v/>
       </c>
       <c r="M5" s="11" t="n"/>

--- a/tests/resources/test_data/TestCases.xlsx
+++ b/tests/resources/test_data/TestCases.xlsx
@@ -7,21 +7,31 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="tc_A5" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="tc_final" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="tc_A4" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="tc_A" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="tc_A3" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="languages" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="preferences" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Sheet4" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="_pattern-old" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="_pattern" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="tc_A15" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="tc_A14" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="tc_A13" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="tc_A12" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="tc_A11" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="tc_A10" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="tc_A9" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="tc_A8" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="tc_A7" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="tc_A6" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="tc_A5" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="tc_final" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="tc_A4" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="tc_A" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="tc_A3" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="languages" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="preferences" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Sheet4" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="_pattern-old" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="_pattern" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'tc_final'!$A$1:$G$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'tc_A4'!$A$1:$G$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'tc_A3'!$A$1:$G$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'tc_final'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'tc_A4'!$A$1:$G$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'tc_A3'!$A$1:$G$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -598,18 +608,113 @@
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentOddEven="0" differentFirst="0">
-    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12 &amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12 Page &amp;P</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="16.81" customWidth="1" style="12" min="1" max="1"/>
+    <col width="15.13" customWidth="1" style="12" min="2" max="2"/>
+    <col width="6.58" customWidth="1" style="12" min="3" max="3"/>
+    <col width="11.25" customWidth="1" style="12" min="4" max="5"/>
+    <col width="8.17" customWidth="1" style="12" min="6" max="6"/>
+    <col width="10.76" customWidth="1" style="12" min="7" max="7"/>
+    <col width="9.16" customWidth="1" style="12" min="10" max="10"/>
+    <col width="9.66" customWidth="1" style="12" min="11" max="12"/>
+    <col width="12.74" customWidth="1" style="12" min="13" max="13"/>
+    <col width="14.83" customWidth="1" style="12" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="12.75" customHeight="1" s="13">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>*** Test Cases ***</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>[Documentation]</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>[Tags]</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>${link}</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>${language}</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>${before}</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>${after}</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="n"/>
+      <c r="J1" s="15" t="inlineStr">
+        <is>
+          <t>RESULT</t>
+        </is>
+      </c>
+      <c r="K1" s="15" t="inlineStr">
+        <is>
+          <t>GOT</t>
+        </is>
+      </c>
+      <c r="L1" s="15" t="inlineStr">
+        <is>
+          <t>DETAILS</t>
+        </is>
+      </c>
+      <c r="M1" s="15" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="N1" s="15" t="inlineStr">
+        <is>
+          <t>SCREENSHOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="12.8" customHeight="1" s="13">
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9370,7 +9475,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19170,7 +19275,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -28962,7 +29067,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37578,7 +37683,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37787,7 +37892,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37895,7 +38000,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="FFFF00FF"/>
@@ -38071,7 +38176,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -47160,4 +47265,939 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="16.81" customWidth="1" style="12" min="1" max="1"/>
+    <col width="15.13" customWidth="1" style="12" min="2" max="2"/>
+    <col width="6.58" customWidth="1" style="12" min="3" max="3"/>
+    <col width="11.25" customWidth="1" style="12" min="4" max="5"/>
+    <col width="8.17" customWidth="1" style="12" min="6" max="6"/>
+    <col width="10.76" customWidth="1" style="12" min="7" max="7"/>
+    <col width="9.16" customWidth="1" style="12" min="10" max="10"/>
+    <col width="9.66" customWidth="1" style="12" min="11" max="12"/>
+    <col width="12.74" customWidth="1" style="12" min="13" max="13"/>
+    <col width="14.83" customWidth="1" style="12" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="12.75" customHeight="1" s="13">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>*** Test Cases ***</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>[Documentation]</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>[Tags]</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>${link}</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>${language}</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>${before}</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>${after}</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="n"/>
+      <c r="J1" s="15" t="inlineStr">
+        <is>
+          <t>RESULT</t>
+        </is>
+      </c>
+      <c r="K1" s="15" t="inlineStr">
+        <is>
+          <t>GOT</t>
+        </is>
+      </c>
+      <c r="L1" s="15" t="inlineStr">
+        <is>
+          <t>DETAILS</t>
+        </is>
+      </c>
+      <c r="M1" s="15" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="N1" s="15" t="inlineStr">
+        <is>
+          <t>SCREENSHOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="12.8" customHeight="1" s="13">
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="16.81" customWidth="1" style="12" min="1" max="1"/>
+    <col width="15.13" customWidth="1" style="12" min="2" max="2"/>
+    <col width="6.58" customWidth="1" style="12" min="3" max="3"/>
+    <col width="11.25" customWidth="1" style="12" min="4" max="5"/>
+    <col width="8.17" customWidth="1" style="12" min="6" max="6"/>
+    <col width="10.76" customWidth="1" style="12" min="7" max="7"/>
+    <col width="9.16" customWidth="1" style="12" min="10" max="10"/>
+    <col width="9.66" customWidth="1" style="12" min="11" max="12"/>
+    <col width="12.74" customWidth="1" style="12" min="13" max="13"/>
+    <col width="14.83" customWidth="1" style="12" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="12.75" customHeight="1" s="13">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>*** Test Cases ***</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>[Documentation]</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>[Tags]</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>${link}</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>${language}</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>${before}</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>${after}</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="n"/>
+      <c r="J1" s="15" t="inlineStr">
+        <is>
+          <t>RESULT</t>
+        </is>
+      </c>
+      <c r="K1" s="15" t="inlineStr">
+        <is>
+          <t>GOT</t>
+        </is>
+      </c>
+      <c r="L1" s="15" t="inlineStr">
+        <is>
+          <t>DETAILS</t>
+        </is>
+      </c>
+      <c r="M1" s="15" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="N1" s="15" t="inlineStr">
+        <is>
+          <t>SCREENSHOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="12.8" customHeight="1" s="13">
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentOddEven="0" differentFirst="0">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12 &amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12 Page &amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="16.81" customWidth="1" style="12" min="1" max="1"/>
+    <col width="15.13" customWidth="1" style="12" min="2" max="2"/>
+    <col width="6.58" customWidth="1" style="12" min="3" max="3"/>
+    <col width="11.25" customWidth="1" style="12" min="4" max="5"/>
+    <col width="8.17" customWidth="1" style="12" min="6" max="6"/>
+    <col width="10.76" customWidth="1" style="12" min="7" max="7"/>
+    <col width="9.16" customWidth="1" style="12" min="10" max="10"/>
+    <col width="9.66" customWidth="1" style="12" min="11" max="12"/>
+    <col width="12.74" customWidth="1" style="12" min="13" max="13"/>
+    <col width="14.83" customWidth="1" style="12" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="12.75" customHeight="1" s="13">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>*** Test Cases ***</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>[Documentation]</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>[Tags]</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>${link}</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>${language}</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>${before}</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>${after}</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="n"/>
+      <c r="J1" s="15" t="inlineStr">
+        <is>
+          <t>RESULT</t>
+        </is>
+      </c>
+      <c r="K1" s="15" t="inlineStr">
+        <is>
+          <t>GOT</t>
+        </is>
+      </c>
+      <c r="L1" s="15" t="inlineStr">
+        <is>
+          <t>DETAILS</t>
+        </is>
+      </c>
+      <c r="M1" s="15" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="N1" s="15" t="inlineStr">
+        <is>
+          <t>SCREENSHOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="12.8" customHeight="1" s="13">
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="16.81" customWidth="1" style="12" min="1" max="1"/>
+    <col width="15.13" customWidth="1" style="12" min="2" max="2"/>
+    <col width="6.58" customWidth="1" style="12" min="3" max="3"/>
+    <col width="11.25" customWidth="1" style="12" min="4" max="5"/>
+    <col width="8.17" customWidth="1" style="12" min="6" max="6"/>
+    <col width="10.76" customWidth="1" style="12" min="7" max="7"/>
+    <col width="9.16" customWidth="1" style="12" min="10" max="10"/>
+    <col width="9.66" customWidth="1" style="12" min="11" max="12"/>
+    <col width="12.74" customWidth="1" style="12" min="13" max="13"/>
+    <col width="14.83" customWidth="1" style="12" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="12.75" customHeight="1" s="13">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>*** Test Cases ***</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>[Documentation]</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>[Tags]</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>${link}</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>${language}</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>${before}</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>${after}</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="n"/>
+      <c r="J1" s="15" t="inlineStr">
+        <is>
+          <t>RESULT</t>
+        </is>
+      </c>
+      <c r="K1" s="15" t="inlineStr">
+        <is>
+          <t>GOT</t>
+        </is>
+      </c>
+      <c r="L1" s="15" t="inlineStr">
+        <is>
+          <t>DETAILS</t>
+        </is>
+      </c>
+      <c r="M1" s="15" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="N1" s="15" t="inlineStr">
+        <is>
+          <t>SCREENSHOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="12.8" customHeight="1" s="13">
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="16.81" customWidth="1" style="12" min="1" max="1"/>
+    <col width="15.13" customWidth="1" style="12" min="2" max="2"/>
+    <col width="6.58" customWidth="1" style="12" min="3" max="3"/>
+    <col width="11.25" customWidth="1" style="12" min="4" max="5"/>
+    <col width="8.17" customWidth="1" style="12" min="6" max="6"/>
+    <col width="10.76" customWidth="1" style="12" min="7" max="7"/>
+    <col width="9.16" customWidth="1" style="12" min="10" max="10"/>
+    <col width="9.66" customWidth="1" style="12" min="11" max="12"/>
+    <col width="12.74" customWidth="1" style="12" min="13" max="13"/>
+    <col width="14.83" customWidth="1" style="12" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="12.75" customHeight="1" s="13">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>*** Test Cases ***</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>[Documentation]</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>[Tags]</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>${link}</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>${language}</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>${before}</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>${after}</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="n"/>
+      <c r="J1" s="15" t="inlineStr">
+        <is>
+          <t>RESULT</t>
+        </is>
+      </c>
+      <c r="K1" s="15" t="inlineStr">
+        <is>
+          <t>GOT</t>
+        </is>
+      </c>
+      <c r="L1" s="15" t="inlineStr">
+        <is>
+          <t>DETAILS</t>
+        </is>
+      </c>
+      <c r="M1" s="15" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="N1" s="15" t="inlineStr">
+        <is>
+          <t>SCREENSHOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="12.8" customHeight="1" s="13">
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="16.81" customWidth="1" style="12" min="1" max="1"/>
+    <col width="15.13" customWidth="1" style="12" min="2" max="2"/>
+    <col width="6.58" customWidth="1" style="12" min="3" max="3"/>
+    <col width="11.25" customWidth="1" style="12" min="4" max="5"/>
+    <col width="8.17" customWidth="1" style="12" min="6" max="6"/>
+    <col width="10.76" customWidth="1" style="12" min="7" max="7"/>
+    <col width="9.16" customWidth="1" style="12" min="10" max="10"/>
+    <col width="9.66" customWidth="1" style="12" min="11" max="12"/>
+    <col width="12.74" customWidth="1" style="12" min="13" max="13"/>
+    <col width="14.83" customWidth="1" style="12" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="12.75" customHeight="1" s="13">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>*** Test Cases ***</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>[Documentation]</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>[Tags]</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>${link}</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>${language}</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>${before}</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>${after}</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="n"/>
+      <c r="J1" s="15" t="inlineStr">
+        <is>
+          <t>RESULT</t>
+        </is>
+      </c>
+      <c r="K1" s="15" t="inlineStr">
+        <is>
+          <t>GOT</t>
+        </is>
+      </c>
+      <c r="L1" s="15" t="inlineStr">
+        <is>
+          <t>DETAILS</t>
+        </is>
+      </c>
+      <c r="M1" s="15" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="N1" s="15" t="inlineStr">
+        <is>
+          <t>SCREENSHOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="12.8" customHeight="1" s="13">
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="16.81" customWidth="1" style="12" min="1" max="1"/>
+    <col width="15.13" customWidth="1" style="12" min="2" max="2"/>
+    <col width="6.58" customWidth="1" style="12" min="3" max="3"/>
+    <col width="11.25" customWidth="1" style="12" min="4" max="5"/>
+    <col width="8.17" customWidth="1" style="12" min="6" max="6"/>
+    <col width="10.76" customWidth="1" style="12" min="7" max="7"/>
+    <col width="9.16" customWidth="1" style="12" min="10" max="10"/>
+    <col width="9.66" customWidth="1" style="12" min="11" max="12"/>
+    <col width="12.74" customWidth="1" style="12" min="13" max="13"/>
+    <col width="14.83" customWidth="1" style="12" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="12.75" customHeight="1" s="13">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>*** Test Cases ***</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>[Documentation]</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>[Tags]</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>${link}</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>${language}</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>${before}</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>${after}</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="n"/>
+      <c r="J1" s="15" t="inlineStr">
+        <is>
+          <t>RESULT</t>
+        </is>
+      </c>
+      <c r="K1" s="15" t="inlineStr">
+        <is>
+          <t>GOT</t>
+        </is>
+      </c>
+      <c r="L1" s="15" t="inlineStr">
+        <is>
+          <t>DETAILS</t>
+        </is>
+      </c>
+      <c r="M1" s="15" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="N1" s="15" t="inlineStr">
+        <is>
+          <t>SCREENSHOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="12.8" customHeight="1" s="13">
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="16.81" customWidth="1" style="12" min="1" max="1"/>
+    <col width="15.13" customWidth="1" style="12" min="2" max="2"/>
+    <col width="6.58" customWidth="1" style="12" min="3" max="3"/>
+    <col width="11.25" customWidth="1" style="12" min="4" max="5"/>
+    <col width="8.17" customWidth="1" style="12" min="6" max="6"/>
+    <col width="10.76" customWidth="1" style="12" min="7" max="7"/>
+    <col width="9.16" customWidth="1" style="12" min="10" max="10"/>
+    <col width="9.66" customWidth="1" style="12" min="11" max="12"/>
+    <col width="12.74" customWidth="1" style="12" min="13" max="13"/>
+    <col width="14.83" customWidth="1" style="12" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="12.75" customHeight="1" s="13">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>*** Test Cases ***</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>[Documentation]</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>[Tags]</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>${link}</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>${language}</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>${before}</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>${after}</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="n"/>
+      <c r="J1" s="15" t="inlineStr">
+        <is>
+          <t>RESULT</t>
+        </is>
+      </c>
+      <c r="K1" s="15" t="inlineStr">
+        <is>
+          <t>GOT</t>
+        </is>
+      </c>
+      <c r="L1" s="15" t="inlineStr">
+        <is>
+          <t>DETAILS</t>
+        </is>
+      </c>
+      <c r="M1" s="15" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="N1" s="15" t="inlineStr">
+        <is>
+          <t>SCREENSHOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="12.8" customHeight="1" s="13">
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="16.81" customWidth="1" style="12" min="1" max="1"/>
+    <col width="15.13" customWidth="1" style="12" min="2" max="2"/>
+    <col width="6.58" customWidth="1" style="12" min="3" max="3"/>
+    <col width="11.25" customWidth="1" style="12" min="4" max="5"/>
+    <col width="8.17" customWidth="1" style="12" min="6" max="6"/>
+    <col width="10.76" customWidth="1" style="12" min="7" max="7"/>
+    <col width="9.16" customWidth="1" style="12" min="10" max="10"/>
+    <col width="9.66" customWidth="1" style="12" min="11" max="12"/>
+    <col width="12.74" customWidth="1" style="12" min="13" max="13"/>
+    <col width="14.83" customWidth="1" style="12" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="12.75" customHeight="1" s="13">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>*** Test Cases ***</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>[Documentation]</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>[Tags]</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>${link}</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>${language}</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>${before}</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>${after}</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="n"/>
+      <c r="J1" s="15" t="inlineStr">
+        <is>
+          <t>RESULT</t>
+        </is>
+      </c>
+      <c r="K1" s="15" t="inlineStr">
+        <is>
+          <t>GOT</t>
+        </is>
+      </c>
+      <c r="L1" s="15" t="inlineStr">
+        <is>
+          <t>DETAILS</t>
+        </is>
+      </c>
+      <c r="M1" s="15" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="N1" s="15" t="inlineStr">
+        <is>
+          <t>SCREENSHOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="12.8" customHeight="1" s="13">
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
 </file>